--- a/verbs.xlsx
+++ b/verbs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yoshimichi/Library/Mobile Documents/com~apple~CloudDocs/Ichikawa/動詞活用くん/github upload用 v1.6/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B770EBB-6734-AA45-B033-A805FC9E89FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E537018-7362-A14F-B53D-18F53BE44C36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1320" yWindow="640" windowWidth="33240" windowHeight="17640" xr2:uid="{A89B81C1-EAA5-FB43-BB76-96C898A6590F}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4817" uniqueCount="3623">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4816" uniqueCount="3631">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1"/>
@@ -13192,6 +13192,50 @@
   </si>
   <si>
     <t>よういした</t>
+  </si>
+  <si>
+    <t>並べる</t>
+    <rPh sb="0" eb="1">
+      <t xml:space="preserve">ナラベル </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ならべる</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>並べない</t>
+    <rPh sb="0" eb="1">
+      <t xml:space="preserve">ナラベナイ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ならべない</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>並べて</t>
+    <rPh sb="0" eb="1">
+      <t xml:space="preserve">ナラベテ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ならべて</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>並べた</t>
+    <rPh sb="0" eb="1">
+      <t xml:space="preserve">ナラベタ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ならべた</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -23122,10 +23166,7 @@
         <v>30</v>
       </c>
       <c r="C190" s="5">
-        <v>1</v>
-      </c>
-      <c r="D190" s="5" t="s">
-        <v>305</v>
+        <v>2</v>
       </c>
       <c r="H190" t="s">
         <v>449</v>
@@ -23140,28 +23181,28 @@
         <v>1098</v>
       </c>
       <c r="L190" t="s">
-        <v>2312</v>
+        <v>3623</v>
       </c>
       <c r="M190" t="s">
-        <v>2313</v>
+        <v>3624</v>
       </c>
       <c r="N190" t="s">
-        <v>2314</v>
+        <v>3625</v>
       </c>
       <c r="O190" t="s">
-        <v>2315</v>
+        <v>3626</v>
       </c>
       <c r="P190" t="s">
-        <v>2316</v>
+        <v>3627</v>
       </c>
       <c r="Q190" t="s">
-        <v>2317</v>
+        <v>3628</v>
       </c>
       <c r="R190" t="s">
-        <v>2318</v>
+        <v>3629</v>
       </c>
       <c r="S190" t="s">
-        <v>2319</v>
+        <v>3630</v>
       </c>
     </row>
     <row r="191" spans="1:19">
